--- a/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A59676E0-E974-4EB3-B7EF-782BC3D2BB3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE38CC72-2E41-451E-9510-91F962FE500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -481,9 +481,6 @@
     <t>bind::db_filter_by_col_3</t>
   </si>
   <si>
-    <t>bind::db_filter_by_col_4</t>
-  </si>
-  <si>
     <t>bind::db_filter_by_col_5</t>
   </si>
   <si>
@@ -605,6 +602,9 @@
   </si>
   <si>
     <t>(Demo) 3. TAS1 LF FTS Form V2</t>
+  </si>
+  <si>
+    <t>col_4</t>
   </si>
 </sst>
 </file>
@@ -1154,7 +1154,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W39"/>
+  <dimension ref="A1:V39"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="1" width="23.5" style="26" customWidth="1"/>
@@ -1172,12 +1172,12 @@
     <col min="13" max="13" width="36.625" style="26" customWidth="1"/>
     <col min="14" max="14" width="11" style="26"/>
     <col min="15" max="15" width="17.75" style="26" bestFit="1" customWidth="1"/>
-    <col min="16" max="20" width="22.125" style="26" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.75" style="26" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11" style="26"/>
+    <col min="16" max="19" width="22.125" style="26" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.75" style="26" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="11" style="26"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="16" customFormat="1" ht="37.5">
+    <row r="1" spans="1:22" s="16" customFormat="1" ht="37.5">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -1238,11 +1238,8 @@
       <c r="T1" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="U1" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:23" s="16" customFormat="1" ht="47.25">
+    </row>
+    <row r="2" spans="1:22" s="16" customFormat="1" ht="47.25">
       <c r="A2" s="28" t="s">
         <v>120</v>
       </c>
@@ -1267,7 +1264,7 @@
       <c r="L2" s="28"/>
       <c r="M2" s="28"/>
     </row>
-    <row r="3" spans="1:23" s="16" customFormat="1">
+    <row r="3" spans="1:22" s="16" customFormat="1">
       <c r="A3" s="16" t="s">
         <v>29</v>
       </c>
@@ -1275,7 +1272,7 @@
         <v>17</v>
       </c>
       <c r="C3" s="30" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D3" s="30"/>
       <c r="E3" s="28"/>
@@ -1288,8 +1285,11 @@
       </c>
       <c r="K3" s="28"/>
       <c r="L3" s="28"/>
-    </row>
-    <row r="4" spans="1:23" s="16" customFormat="1">
+      <c r="T3" s="16" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22" s="16" customFormat="1">
       <c r="A4" s="16" t="s">
         <v>29</v>
       </c>
@@ -1297,7 +1297,7 @@
         <v>143</v>
       </c>
       <c r="C4" s="30" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D4" s="30"/>
       <c r="E4" s="28"/>
@@ -1310,22 +1310,22 @@
       </c>
       <c r="K4" s="28"/>
       <c r="L4" s="28"/>
-      <c r="Q4" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="U4" s="16" t="s">
+      <c r="P4" s="16" t="s">
+        <v>152</v>
+      </c>
+      <c r="T4" s="16" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:23" s="16" customFormat="1">
+    <row r="5" spans="1:22" s="16" customFormat="1">
       <c r="A5" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B5" s="29" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D5" s="30"/>
       <c r="E5" s="28"/>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="K5" s="28"/>
       <c r="L5" s="28"/>
-      <c r="R5" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="U5" s="16" t="s">
+      <c r="Q5" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="T5" s="16" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="6" spans="1:23" s="16" customFormat="1">
+    <row r="6" spans="1:22" s="16" customFormat="1">
       <c r="A6" s="16" t="s">
         <v>29</v>
       </c>
       <c r="B6" s="29" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C6" s="30" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D6" s="30"/>
       <c r="E6" s="28"/>
@@ -1366,14 +1366,14 @@
       </c>
       <c r="K6" s="28"/>
       <c r="L6" s="28"/>
-      <c r="S6" s="16" t="s">
-        <v>186</v>
-      </c>
-      <c r="U6" s="16" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" s="16" customFormat="1">
+      <c r="R6" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="T6" s="16" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="16" customFormat="1">
       <c r="A7" s="10" t="s">
         <v>31</v>
       </c>
@@ -1394,12 +1394,12 @@
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
     </row>
-    <row r="8" spans="1:23" s="16" customFormat="1">
+    <row r="8" spans="1:22" s="16" customFormat="1">
       <c r="A8" s="17" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" s="19" t="s">
         <v>100</v>
@@ -1416,7 +1416,7 @@
       <c r="M8" s="17"/>
       <c r="N8" s="22"/>
     </row>
-    <row r="9" spans="1:23" s="16" customFormat="1">
+    <row r="9" spans="1:22" s="16" customFormat="1">
       <c r="A9" s="10" t="s">
         <v>31</v>
       </c>
@@ -1437,7 +1437,7 @@
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
     </row>
-    <row r="10" spans="1:23" s="16" customFormat="1">
+    <row r="10" spans="1:22" s="16" customFormat="1">
       <c r="A10" s="10" t="s">
         <v>31</v>
       </c>
@@ -1458,15 +1458,15 @@
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
     </row>
-    <row r="11" spans="1:23" s="16" customFormat="1">
+    <row r="11" spans="1:22" s="16" customFormat="1">
       <c r="A11" s="16" t="s">
+        <v>166</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>177</v>
+      </c>
+      <c r="C11" s="38" t="s">
         <v>167</v>
-      </c>
-      <c r="B11" s="38" t="s">
-        <v>178</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>168</v>
       </c>
       <c r="D11" s="38"/>
       <c r="G11" s="38"/>
@@ -1475,24 +1475,24 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:23" s="38" customFormat="1" ht="31.5">
+    <row r="12" spans="1:22" s="38" customFormat="1" ht="31.5">
       <c r="A12" s="38" t="s">
         <v>131</v>
       </c>
       <c r="B12" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C12" s="38" t="s">
+        <v>168</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>169</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>170</v>
+      </c>
+      <c r="H12" s="38" t="s">
         <v>179</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>169</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>170</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>180</v>
       </c>
       <c r="J12" s="38" t="s">
         <v>16</v>
@@ -1504,54 +1504,53 @@
       <c r="T12" s="16"/>
       <c r="U12" s="16"/>
       <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-    </row>
-    <row r="13" spans="1:23" s="16" customFormat="1">
+    </row>
+    <row r="13" spans="1:22" s="16" customFormat="1">
       <c r="A13" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C13" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="D13" s="38" t="s">
         <v>172</v>
-      </c>
-      <c r="D13" s="38" t="s">
-        <v>173</v>
       </c>
       <c r="G13" s="38"/>
       <c r="H13" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J13" s="38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:23" s="16" customFormat="1" ht="31.5">
+    <row r="14" spans="1:22" s="16" customFormat="1" ht="31.5">
       <c r="A14" s="16" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D14" s="38"/>
       <c r="F14" s="16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H14" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J14" s="38" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:23" s="16" customFormat="1" ht="47.25">
+    <row r="15" spans="1:22" s="16" customFormat="1" ht="47.25">
       <c r="A15" s="16" t="s">
         <v>18</v>
       </c>
@@ -1559,20 +1558,20 @@
         <v>19</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D15" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F15" s="16" t="s">
         <v>101</v>
       </c>
       <c r="G15" s="16" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H15" s="38"/>
       <c r="I15" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J15" s="38" t="s">
         <v>16</v>
@@ -1581,7 +1580,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:23" s="16" customFormat="1">
+    <row r="16" spans="1:22" s="16" customFormat="1">
       <c r="A16" s="28" t="s">
         <v>18</v>
       </c>
@@ -1644,7 +1643,7 @@
       <c r="F18" s="28"/>
       <c r="G18" s="32"/>
       <c r="H18" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="I18" s="29"/>
       <c r="J18" s="28" t="s">
@@ -1669,7 +1668,7 @@
       <c r="F19" s="28"/>
       <c r="G19" s="32"/>
       <c r="H19" s="29" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="I19" s="29"/>
       <c r="J19" s="28" t="s">
@@ -1740,7 +1739,7 @@
       <c r="F22" s="28"/>
       <c r="G22" s="32"/>
       <c r="H22" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I22" s="28"/>
       <c r="J22" s="28" t="s">
@@ -1767,7 +1766,7 @@
       <c r="F23" s="33"/>
       <c r="G23" s="35"/>
       <c r="H23" s="29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="I23" s="33"/>
       <c r="J23" s="28" t="s">
@@ -1794,7 +1793,7 @@
       <c r="F24" s="33"/>
       <c r="G24" s="35"/>
       <c r="H24" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="I24" s="33"/>
       <c r="J24" s="28" t="s">
@@ -1821,7 +1820,7 @@
       <c r="F25" s="33"/>
       <c r="G25" s="35"/>
       <c r="H25" s="29" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="I25" s="33"/>
       <c r="J25" s="28" t="s">
@@ -3697,10 +3696,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="16" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="26" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C2" s="26" t="s">
         <v>91</v>

--- a/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE38CC72-2E41-451E-9510-91F962FE500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAC5377-9B70-45A6-A2B9-4B96B35DC6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="189">
   <si>
     <t>type</t>
   </si>
@@ -1887,7 +1887,9 @@
       <c r="C29" s="36" t="s">
         <v>108</v>
       </c>
-      <c r="H29" s="38"/>
+      <c r="H29" s="29" t="s">
+        <v>106</v>
+      </c>
       <c r="I29" s="27"/>
     </row>
     <row r="30" spans="1:13">

--- a/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DAC5377-9B70-45A6-A2B9-4B96B35DC6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8C43357-AEF9-4A28-AC3B-6A2ED52803B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="190">
   <si>
     <t>type</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>col_4</t>
+  </si>
+  <si>
+    <t>bind::type</t>
   </si>
 </sst>
 </file>
@@ -1238,6 +1241,9 @@
       <c r="T1" s="1" t="s">
         <v>148</v>
       </c>
+      <c r="U1" s="16" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="2" spans="1:22" s="16" customFormat="1" ht="47.25">
       <c r="A2" s="28" t="s">
@@ -1393,6 +1399,9 @@
       <c r="K7" s="10"/>
       <c r="L7" s="10"/>
       <c r="M7" s="10"/>
+      <c r="U7" s="16" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:22" s="16" customFormat="1">
       <c r="A8" s="17" t="s">
@@ -1436,6 +1445,9 @@
       <c r="K9" s="10"/>
       <c r="L9" s="10"/>
       <c r="M9" s="10"/>
+      <c r="U9" s="16" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="10" spans="1:22" s="16" customFormat="1">
       <c r="A10" s="10" t="s">
@@ -1457,6 +1469,9 @@
       <c r="K10" s="10"/>
       <c r="L10" s="10"/>
       <c r="M10" s="10"/>
+      <c r="U10" s="16" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="11" spans="1:22" s="16" customFormat="1">
       <c r="A11" s="16" t="s">

--- a/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
+++ b/Demo/lf/demo_lf_tas_9999_3_fts.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\Demo\lf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB8019D-42B9-4623-9F30-5E93EF78095A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E86CCF8D-B6E1-4702-8399-C82B1794C1F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -555,9 +555,6 @@
     <t>ID Codes generated (from the participant form)</t>
   </si>
   <si>
-    <t>d2507</t>
-  </si>
-  <si>
     <t>select_one recorder_list</t>
   </si>
   <si>
@@ -709,6 +706,9 @@
        )
 	  )
 	 )</t>
+  </si>
+  <si>
+    <t>d9999</t>
   </si>
 </sst>
 </file>
@@ -760,7 +760,7 @@
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1355,7 +1355,7 @@
     </row>
     <row r="2" spans="1:20" s="5" customFormat="1" ht="47.25">
       <c r="A2" s="24" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B2" s="26" t="s">
         <v>95</v>
@@ -1390,10 +1390,10 @@
         <v>17</v>
       </c>
       <c r="B3" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C3" s="27" t="s">
         <v>184</v>
-      </c>
-      <c r="C3" s="27" t="s">
-        <v>185</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="24"/>
@@ -1422,10 +1422,10 @@
         <v>17</v>
       </c>
       <c r="B4" s="26" t="s">
+        <v>185</v>
+      </c>
+      <c r="C4" s="27" t="s">
         <v>186</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>187</v>
       </c>
       <c r="D4" s="27"/>
       <c r="E4" s="24"/>
@@ -1445,7 +1445,7 @@
         <v>92</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="R4" s="24"/>
       <c r="S4" s="24"/>
@@ -1456,10 +1456,10 @@
         <v>17</v>
       </c>
       <c r="B5" s="26" t="s">
+        <v>187</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>188</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>189</v>
       </c>
       <c r="D5" s="27"/>
       <c r="E5" s="24"/>
@@ -1476,11 +1476,11 @@
       <c r="N5" s="24"/>
       <c r="O5" s="24"/>
       <c r="P5" s="24" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="Q5" s="24"/>
       <c r="R5" s="24" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="S5" s="24"/>
       <c r="T5" s="24"/>
@@ -1490,10 +1490,10 @@
         <v>17</v>
       </c>
       <c r="B6" s="26" t="s">
+        <v>189</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>190</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>191</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="24"/>
@@ -1515,7 +1515,7 @@
       <c r="Q6" s="24"/>
       <c r="R6" s="24"/>
       <c r="S6" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="T6" s="24"/>
     </row>
@@ -1658,7 +1658,7 @@
         <v>80</v>
       </c>
       <c r="B12" s="29" t="s">
-        <v>177</v>
+        <v>226</v>
       </c>
       <c r="C12" s="29" t="s">
         <v>81</v>
@@ -1778,7 +1778,7 @@
       <c r="F16" s="14"/>
       <c r="G16" s="14"/>
       <c r="H16" s="15" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="15"/>
@@ -1794,7 +1794,7 @@
       <c r="R16" s="31"/>
       <c r="S16" s="31"/>
       <c r="T16" s="41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="17" spans="1:20" s="5" customFormat="1">
@@ -1834,7 +1834,7 @@
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
       <c r="H18" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="I18" s="11"/>
       <c r="J18" s="11" t="s">
@@ -1866,7 +1866,7 @@
       <c r="F19" s="42"/>
       <c r="G19" s="12"/>
       <c r="H19" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I19" s="11"/>
       <c r="J19" s="11" t="s">
@@ -1898,7 +1898,7 @@
       <c r="F20" s="42"/>
       <c r="G20" s="12"/>
       <c r="H20" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I20" s="11"/>
       <c r="J20" s="11" t="s">
@@ -1934,7 +1934,7 @@
         <v>119</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="I21" s="11"/>
       <c r="J21" s="11" t="s">
@@ -2112,7 +2112,7 @@
       <c r="F27" s="24"/>
       <c r="G27" s="43"/>
       <c r="H27" s="26" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I27" s="26"/>
       <c r="J27" s="24" t="s">
@@ -2144,7 +2144,7 @@
       <c r="F28" s="24"/>
       <c r="G28" s="43"/>
       <c r="H28" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="I28" s="26"/>
       <c r="J28" s="24" t="s">
@@ -2198,7 +2198,7 @@
       <c r="F30" s="24"/>
       <c r="G30" s="43"/>
       <c r="H30" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I30" s="24"/>
       <c r="J30" s="24"/>
@@ -2232,7 +2232,7 @@
         <v>21</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I31" s="24"/>
       <c r="J31" s="24"/>
@@ -2262,7 +2262,7 @@
       <c r="F32" s="33"/>
       <c r="G32" s="44"/>
       <c r="H32" s="26" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I32" s="33"/>
       <c r="J32" s="24" t="s">
@@ -2294,7 +2294,7 @@
       <c r="F33" s="33"/>
       <c r="G33" s="44"/>
       <c r="H33" s="26" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="I33" s="33"/>
       <c r="J33" s="24" t="s">
@@ -2326,7 +2326,7 @@
       <c r="F34" s="33"/>
       <c r="G34" s="44"/>
       <c r="H34" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="I34" s="33"/>
       <c r="J34" s="24" t="s">
@@ -2348,10 +2348,10 @@
         <v>27</v>
       </c>
       <c r="B35" s="33" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="34" t="s">
         <v>195</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>196</v>
       </c>
       <c r="D35" s="44"/>
       <c r="E35" s="33"/>
@@ -2359,7 +2359,7 @@
       <c r="G35" s="44"/>
       <c r="H35" s="26"/>
       <c r="I35" s="26" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="J35" s="33" t="s">
         <v>16</v>
@@ -2382,17 +2382,17 @@
         <v>30</v>
       </c>
       <c r="B36" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="C36" s="34" t="s">
         <v>197</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>198</v>
       </c>
       <c r="D36" s="44"/>
       <c r="E36" s="33"/>
       <c r="F36" s="33"/>
       <c r="G36" s="44"/>
       <c r="H36" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I36" s="26"/>
       <c r="J36" s="33"/>
@@ -2412,17 +2412,17 @@
         <v>13</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C37" s="34" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D37" s="44"/>
       <c r="E37" s="33"/>
       <c r="F37" s="33"/>
       <c r="G37" s="44"/>
       <c r="H37" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I37" s="26"/>
       <c r="J37" s="33" t="s">
@@ -2444,17 +2444,17 @@
         <v>17</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C38" s="34" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D38" s="44"/>
       <c r="E38" s="33"/>
       <c r="F38" s="33"/>
       <c r="G38" s="44"/>
       <c r="H38" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I38" s="26"/>
       <c r="J38" s="33" t="s">
@@ -2476,17 +2476,17 @@
         <v>96</v>
       </c>
       <c r="B39" s="33" t="s">
+        <v>199</v>
+      </c>
+      <c r="C39" s="34" t="s">
         <v>200</v>
-      </c>
-      <c r="C39" s="34" t="s">
-        <v>201</v>
       </c>
       <c r="D39" s="44"/>
       <c r="E39" s="33"/>
       <c r="F39" s="33"/>
       <c r="G39" s="44"/>
       <c r="H39" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I39" s="26"/>
       <c r="J39" s="33" t="s">
@@ -2508,17 +2508,17 @@
         <v>13</v>
       </c>
       <c r="B40" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="C40" s="34" t="s">
         <v>202</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>203</v>
       </c>
       <c r="D40" s="44"/>
       <c r="E40" s="33"/>
       <c r="F40" s="33"/>
       <c r="G40" s="44"/>
       <c r="H40" s="26" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="I40" s="26"/>
       <c r="J40" s="33" t="s">
@@ -2540,17 +2540,17 @@
         <v>96</v>
       </c>
       <c r="B41" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C41" s="34" t="s">
         <v>204</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>205</v>
       </c>
       <c r="D41" s="44"/>
       <c r="E41" s="33"/>
       <c r="F41" s="33"/>
       <c r="G41" s="44"/>
       <c r="H41" s="26" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I41" s="26"/>
       <c r="J41" s="33" t="s">
@@ -2572,17 +2572,17 @@
         <v>96</v>
       </c>
       <c r="B42" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="C42" s="34" t="s">
         <v>206</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>207</v>
       </c>
       <c r="D42" s="44"/>
       <c r="E42" s="33"/>
       <c r="F42" s="33"/>
       <c r="G42" s="44"/>
       <c r="H42" s="26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="I42" s="26"/>
       <c r="J42" s="33" t="s">
@@ -2614,7 +2614,7 @@
       <c r="F43" s="33"/>
       <c r="G43" s="44"/>
       <c r="H43" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I43" s="24"/>
       <c r="J43" s="33"/>
@@ -2644,7 +2644,7 @@
       <c r="F44" s="33"/>
       <c r="G44" s="44"/>
       <c r="H44" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I44" s="24"/>
       <c r="J44" s="33" t="s">
@@ -2676,7 +2676,7 @@
       <c r="F45" s="33"/>
       <c r="G45" s="44"/>
       <c r="H45" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I45" s="33"/>
       <c r="J45" s="33" t="s">
@@ -2708,7 +2708,7 @@
       <c r="F46" s="33"/>
       <c r="G46" s="44"/>
       <c r="H46" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I46" s="33"/>
       <c r="J46" s="33" t="s">
@@ -2740,7 +2740,7 @@
       <c r="F47" s="33"/>
       <c r="G47" s="44"/>
       <c r="H47" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="I47" s="33"/>
       <c r="J47" s="33" t="s">
@@ -3210,7 +3210,7 @@
     </row>
     <row r="20" spans="1:3" s="8" customFormat="1">
       <c r="A20" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B20" s="18" t="s">
         <v>68</v>
@@ -3221,7 +3221,7 @@
     </row>
     <row r="21" spans="1:3" s="8" customFormat="1">
       <c r="A21" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B21" s="18" t="s">
         <v>69</v>
@@ -3232,7 +3232,7 @@
     </row>
     <row r="22" spans="1:3" s="8" customFormat="1">
       <c r="A22" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>70</v>
@@ -3243,7 +3243,7 @@
     </row>
     <row r="23" spans="1:3" s="8" customFormat="1">
       <c r="A23" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B23" s="18" t="s">
         <v>71</v>
@@ -3254,13 +3254,13 @@
     </row>
     <row r="24" spans="1:3" s="8" customFormat="1">
       <c r="A24" s="20" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B24" s="18">
         <v>99</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:3" s="8" customFormat="1">
@@ -3317,10 +3317,10 @@
         <v>141</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -3445,10 +3445,10 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C2" t="s">
         <v>78</v>
